--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2756-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2756-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFA6F7B4-7A1F-42D0-AF1A-6417275A149E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCB07547-79E5-4BDD-9B02-18DE2456A26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{226F2300-BC00-4883-873F-98D0500E286F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{233606FF-F20D-439A-98C7-09520A72FE00}"/>
   </bookViews>
   <sheets>
     <sheet name="2756-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1595,23 +1595,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5D037A-B154-410E-808A-B14AAA2C8239}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64CFA82A-FBA1-4BC4-B21F-E62BC99A375E}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" customWidth="1"/>
-    <col min="7" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1639,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1669,7 +1669,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1765,7 +1765,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>2025</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <v>2024</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="43">
         <v>2023</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="45" t="s">
         <v>26</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="46"/>
       <c r="B23" s="22" t="s">
         <v>39</v>
@@ -2787,7 +2787,7 @@
       <c r="Q23" s="50"/>
       <c r="R23" s="50"/>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="41">
         <v>2022</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="55" t="s">
         <v>26</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="24" t="s">
         <v>44</v>
@@ -3143,7 +3143,7 @@
       <c r="Q30" s="60"/>
       <c r="R30" s="60"/>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="43">
         <v>2021</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>26</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>26</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>26</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="41">
         <v>2020</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>26</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>26</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="43">
         <v>2019</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>26</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>26</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="41" t="s">
         <v>59</v>
       </c>
